--- a/out/LSTM-Mamba1_repeat_4_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002047988586127758</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001388927106745541</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0009900096338242292</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0007554821204394102</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0006206762045621872</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.000536787323653698</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0004906880203634501</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0004650549963116646</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0004492534790188074</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0004352177493274212</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0004148208536207676</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0004022251814603806</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0003944211639463902</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0004026168026030064</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0004046962130814791</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.00039707962423563</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0003859382122755051</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0003843419253826141</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0003927215002477169</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0004117025528103113</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0004205072764307261</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0004151277244091034</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0004018938634544611</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.000394417904317379</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0003998256288468838</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0004081688821315765</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0004522665403783321</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0005055421497672796</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0005448113661259413</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0005670173559337854</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0005878543015569448</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0005978813860565424</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0005992469377815723</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0006041489541530609</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0006226333789527416</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0006430377252399921</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0006576033774763346</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0006802426651120186</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0006986060179769993</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0007143823895603418</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0007332926616072655</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0007936614565551281</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0009208754636347294</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001093017868697643</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001191553892567754</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001206748420372605</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001230980269610882</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.00128703354857862</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001332468120381236</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001413383870385587</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.00149581441655755</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001558464951813221</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001682149944826961</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001875400892458856</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002103338483721018</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002297591883689165</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002554014790803194</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002801630180329084</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003057644702494144</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003278505988419056</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003427884774282575</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003554037073627114</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003537424374371767</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.003472922137007117</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.003416524967178702</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003385653020814061</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003428070107474923</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.00345898512750864</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.003543790895491838</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00363785051740706</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003675327636301517</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003600418101996183</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00350695219822228</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003342670621350408</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003200852544978261</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003100286470726132</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003050456289201975</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002993219532072544</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002949652029201388</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002927868161350489</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002968019340187311</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003055768087506294</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003165715606883168</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003283012891188264</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003354398533701897</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003385378513485193</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003426071023568511</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003476137528195977</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003497432451695204</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003493499476462603</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003489780705422163</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003493915079161525</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003456489415839314</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003384507726877928</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00331541383638978</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003289424814283848</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003306626109406352</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003299794858321548</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003240022342652082</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.00315533229149878</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003037966322153807</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002948430133983493</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002872038632631302</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.002787822857499123</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002699379343539476</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.002614656230434775</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002498884219676256</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002393242903053761</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002326635643839836</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002294121077284217</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002273583551868796</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002224061638116837</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002188806654885411</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002184829441830516</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002188696525990963</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002190218307077885</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002212972845882177</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002307253889739513</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002373398980125785</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002391007263213396</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002370778005570173</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002349945716559887</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002302683889865875</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00226262304931879</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002246567513793707</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000006.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.002047988586127758</v>
+        <v>-0.002047988120466471</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.01999999999999985</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.001388927106745541</v>
+        <v>-0.001388926175422966</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1200000000000001</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.0009900096338242292</v>
+        <v>-0.0009900089353322983</v>
       </c>
       <c r="JB4" t="n">
         <v>0.8599999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.0007554821204394102</v>
+        <v>-0.0007554790936410427</v>
       </c>
       <c r="JB5" t="n">
         <v>0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0006206762045621872</v>
+        <v>-0.0006206706166267395</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.000536787323653698</v>
+        <v>-0.0005367842968553305</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0004906880203634501</v>
+        <v>-0.0004906868562102318</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0004650549963116646</v>
+        <v>-0.0004650563932955265</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0004492534790188074</v>
+        <v>-0.0004492541775107384</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0004022251814603806</v>
+        <v>-0.0004022249486297369</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0003944211639463902</v>
+        <v>-0.0003944227937608957</v>
       </c>
       <c r="JB14" t="n">
         <v>0.3999999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0004026168026030064</v>
+        <v>-0.0004026140086352825</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3999999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0004046962130814791</v>
+        <v>-0.0004046941176056862</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.00039707962423563</v>
+        <v>-0.0003970791585743427</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0003859382122755051</v>
+        <v>-0.0003859379794448614</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0003843419253826141</v>
+        <v>-0.0003843437880277634</v>
       </c>
       <c r="JB19" t="n">
         <v>0.2599999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0003927215002477169</v>
+        <v>-0.0003927233628928661</v>
       </c>
       <c r="JB20" t="n">
         <v>0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0004117025528103113</v>
+        <v>-0.0004117039497941732</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0004205072764307261</v>
+        <v>-0.0004205103032290936</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0004018938634544611</v>
+        <v>-0.0004018947947770357</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.000394417904317379</v>
+        <v>-0.0003944144118577242</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0003998256288468838</v>
+        <v>-0.0003998239990323782</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0004081688821315765</v>
+        <v>-0.0004081698134541512</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.02000000000000007</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0004522665403783321</v>
+        <v>-0.0004522672388702631</v>
       </c>
       <c r="JB28" t="n">
         <v>0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0005055421497672796</v>
+        <v>-0.000505541916936636</v>
       </c>
       <c r="JB29" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.0005448113661259413</v>
+        <v>-0.0005448125302791595</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0005670173559337854</v>
+        <v>-0.0005670171231031418</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0005878543015569448</v>
+        <v>-0.0005878547672182322</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0005978813860565424</v>
+        <v>-0.0005978816188871861</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.8599999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0006041489541530609</v>
+        <v>-0.0006041515152901411</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0006226333789527416</v>
+        <v>-0.0006226357072591782</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0006430377252399921</v>
+        <v>-0.000643039820715785</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0006576033774763346</v>
+        <v>-0.0006576040759682655</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0006802426651120186</v>
+        <v>-0.0006802382413297892</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0006986060179769993</v>
+        <v>-0.0006986041553318501</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0007143823895603418</v>
+        <v>-0.0007143798284232616</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0007332926616072655</v>
+        <v>-0.0007332914974540472</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0009208754636347294</v>
+        <v>-0.0009208777919411659</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.001093017868697643</v>
+        <v>-0.001093018334358931</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.001191553892567754</v>
+        <v>-0.001191553543321788</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001206748420372605</v>
+        <v>-0.001206748886033893</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001230980269610882</v>
+        <v>-0.001230980735272169</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.00128703354857862</v>
+        <v>-0.001287033781409264</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001332468120381236</v>
+        <v>-0.001332468469627202</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001413383870385587</v>
+        <v>-0.001413384103216231</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.00149581441655755</v>
+        <v>-0.001495814882218838</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001558464951813221</v>
+        <v>-0.001558466348797083</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001682149944826961</v>
+        <v>-0.00168214796576649</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001875400892458856</v>
+        <v>-0.001875400776043534</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.002103338483721018</v>
+        <v>-0.002103340113535523</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002297591883689165</v>
+        <v>-0.002297590486705303</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.002554014790803194</v>
+        <v>-0.002554022707045078</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.002801630180329084</v>
+        <v>-0.002801644382998347</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003057644702494144</v>
+        <v>-0.003057664493098855</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003278505988419056</v>
+        <v>-0.00327851390466094</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.003427884774282575</v>
+        <v>-0.003427891759201884</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.003554037073627114</v>
+        <v>-0.003554034978151321</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.003537424374371767</v>
+        <v>-0.003537426237016916</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.003472922137007117</v>
+        <v>-0.003472915850579739</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.003416524967178702</v>
+        <v>-0.003416523803025484</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.003385653020814061</v>
+        <v>-0.003385653719305992</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003428070107474923</v>
+        <v>-0.003428070340305567</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.00345898512750864</v>
+        <v>-0.003459005616605282</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.003543790895491838</v>
+        <v>-0.003543800208717585</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00363785051740706</v>
+        <v>-0.003637857967987657</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003675327636301517</v>
+        <v>-0.003675336018204689</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003600418101996183</v>
+        <v>-0.00360042043030262</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.00350695219822228</v>
+        <v>-0.003506967797875404</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.003342670621350408</v>
+        <v>-0.003342680167406797</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003200852544978261</v>
+        <v>-0.003200857201591134</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003100286470726132</v>
+        <v>-0.00310029718093574</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003050456289201975</v>
+        <v>-0.003050459083169699</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002993219532072544</v>
+        <v>-0.002993216272443533</v>
       </c>
       <c r="JB79" t="n">
         <v>0.02000000000000007</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002949652029201388</v>
+        <v>-0.002949651330709457</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002927868161350489</v>
+        <v>-0.002927864203229547</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002968019340187311</v>
+        <v>-0.002968014217913151</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003055768087506294</v>
+        <v>-0.003055766923353076</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.003165715606883168</v>
+        <v>-0.003165718866512179</v>
       </c>
       <c r="JB84" t="n">
         <v>0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003283012891188264</v>
+        <v>-0.003283021040260792</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003354398533701897</v>
+        <v>-0.003354402724653482</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.8599999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003385378513485193</v>
+        <v>-0.003385382005944848</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003426071023568511</v>
+        <v>-0.003426074748858809</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003476137528195977</v>
+        <v>-0.00347613962367177</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003497432451695204</v>
+        <v>-0.003497433150187135</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.003493499476462603</v>
+        <v>-0.003493505297228694</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003489780705422163</v>
+        <v>-0.003489790484309196</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003493915079161525</v>
+        <v>-0.003493928583338857</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.8599999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003456489415839314</v>
+        <v>-0.003456507110968232</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.1199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003384507726877928</v>
+        <v>-0.003384523559361696</v>
       </c>
       <c r="JB95" t="n">
         <v>0.02000000000000007</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00331541383638978</v>
+        <v>-0.003315422218292952</v>
       </c>
       <c r="JB96" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.003289424814283848</v>
+        <v>-0.003289437387138605</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.003306626109406352</v>
+        <v>-0.003306637052446604</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.003299794858321548</v>
+        <v>-0.003299797186627984</v>
       </c>
       <c r="JB99" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.003240022342652082</v>
+        <v>-0.003240020014345646</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.00315533229149878</v>
+        <v>-0.003155335551127791</v>
       </c>
       <c r="JB101" t="n">
         <v>0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003037966322153807</v>
+        <v>-0.003037959104403853</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002948430133983493</v>
+        <v>-0.002948423614725471</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002872038632631302</v>
+        <v>-0.002872041426599026</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.002787822857499123</v>
+        <v>-0.002787821926176548</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.002699379343539476</v>
+        <v>-0.002699378645047545</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.002614656230434775</v>
+        <v>-0.002614658558741212</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.002498884219676256</v>
+        <v>-0.002498884918168187</v>
       </c>
       <c r="JB108" t="n">
         <v>0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002393242903053761</v>
+        <v>-0.00239324220456183</v>
       </c>
       <c r="JB109" t="n">
         <v>0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002326635643839836</v>
+        <v>-0.002326636807993054</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002294121077284217</v>
+        <v>-0.002294124336913228</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002273583551868796</v>
+        <v>-0.002273587277159095</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002224061638116837</v>
+        <v>-0.002224066760390997</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002188806654885411</v>
+        <v>-0.002188809681683779</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002184829441830516</v>
+        <v>-0.002184835029765964</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002188696525990963</v>
+        <v>-0.002188700484111905</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002190218307077885</v>
+        <v>-0.002190225757658482</v>
       </c>
       <c r="JB117" t="n">
         <v>0.2599999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002212972845882177</v>
+        <v>-0.002212975872680545</v>
       </c>
       <c r="JB118" t="n">
         <v>0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002307253889739513</v>
+        <v>-0.002307259244844317</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002373398980125785</v>
+        <v>-0.002373400842770934</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002391007263213396</v>
+        <v>-0.002391011454164982</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002370778005570173</v>
+        <v>-0.002370784990489483</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002349945716559887</v>
+        <v>-0.002349953632801771</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002302683889865875</v>
+        <v>-0.002302689710631967</v>
       </c>
       <c r="JB124" t="n">
         <v>0.1199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.00226262304931879</v>
+        <v>-0.002262626308947802</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9299999999999999</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002246567513793707</v>
+        <v>-0.002246569842100143</v>
       </c>
       <c r="JB126" t="n">
         <v>1.14</v>
